--- a/exports/BLUESTARCO_full_report.xlsx
+++ b/exports/BLUESTARCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.56</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>499</v>
+        <v>497.4</v>
       </c>
       <c r="I2" t="n">
         <v>497.4325191712755</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>1.02</v>
+        <v>0.7</v>
       </c>
       <c r="L2" t="n">
         <v>2.25</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>5.52</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>461.5</v>
+        <v>500.8</v>
       </c>
       <c r="I3" t="n">
         <v>463.264861019514</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>7.22</v>
+        <v>-0.68</v>
       </c>
       <c r="L3" t="n">
-        <v>0.51</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>0.15</v>
+        <v>1.41</v>
       </c>
       <c r="N3" t="n">
-        <v>5.73</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>-0.8</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>12.47</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>510</v>
+        <v>500.55</v>
       </c>
       <c r="I4" t="n">
         <v>506.5546981294811</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>1.84</v>
+        <v>-0.05</v>
       </c>
       <c r="L4" t="n">
         <v>7.78</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44649.55208333334</v>
+        <v>44650.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>516.55</v>
+        <v>528</v>
       </c>
       <c r="I5" t="n">
         <v>524.666228325955</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.2</v>
+        <v>-5.48</v>
       </c>
       <c r="L5" t="n">
-        <v>4.57</v>
+        <v>6.66</v>
       </c>
       <c r="M5" t="n">
         <v>2.73</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.25</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.38541666666</v>
+        <v>44686.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>553.55</v>
+        <v>547.9</v>
       </c>
       <c r="I6" t="n">
         <v>550.4031910341591</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>4.84</v>
+        <v>3.77</v>
       </c>
       <c r="L6" t="n">
         <v>1.78</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44753.38541666666</v>
+        <v>44753.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>455.65</v>
+        <v>475.5</v>
       </c>
       <c r="I7" t="n">
         <v>465.5957610938673</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>66.83333333333333</v>
+        <v>67</v>
       </c>
       <c r="K7" t="n">
-        <v>16.84</v>
+        <v>13.21</v>
       </c>
       <c r="L7" t="n">
         <v>6.34</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>548.75</v>
+        <v>528</v>
       </c>
       <c r="I8" t="n">
         <v>535.5098716157136</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>69.83333333333333</v>
+        <v>70</v>
       </c>
       <c r="K8" t="n">
-        <v>15.4</v>
+        <v>11.04</v>
       </c>
       <c r="L8" t="n">
         <v>4.94</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>10.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44844.55208333334</v>
+        <v>44845.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>578.35</v>
+        <v>586.4</v>
       </c>
       <c r="I9" t="n">
         <v>581.506273966462</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.539999999999999</v>
+        <v>-11.06</v>
       </c>
       <c r="L9" t="n">
-        <v>10.17</v>
+        <v>12.29</v>
       </c>
       <c r="M9" t="n">
         <v>1.51</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.22</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44880.55208333334</v>
+        <v>44881.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>599.5</v>
+        <v>589</v>
       </c>
       <c r="I10" t="n">
         <v>589.6923164318758</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n">
-        <v>2.23</v>
+        <v>0.44</v>
       </c>
       <c r="L10" t="n">
         <v>3.16</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.77</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44890.55208333334</v>
+        <v>44893.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>605.3</v>
+        <v>610.5</v>
       </c>
       <c r="I11" t="n">
         <v>605.594563788221</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.77</v>
+        <v>-3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>3.17</v>
+        <v>4.84</v>
       </c>
       <c r="M11" t="n">
         <v>0.62</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>5.74</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>622.5</v>
+        <v>602.5</v>
       </c>
       <c r="I12" t="n">
         <v>603.068494017468</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>1.97</v>
+        <v>-1.31</v>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.84</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>3.21</v>
       </c>
       <c r="O12" t="n">
         <v>0.78</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>8.6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44936.55208333334</v>
+        <v>44937.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>608.5</v>
+        <v>625.45</v>
       </c>
       <c r="I13" t="n">
         <v>625.2662387144695</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-1</v>
+        <v>-3.81</v>
       </c>
       <c r="L13" t="n">
-        <v>2.33</v>
+        <v>4.17</v>
       </c>
       <c r="M13" t="n">
         <v>1.61</v>
       </c>
       <c r="N13" t="n">
-        <v>1.74</v>
+        <v>2.53</v>
       </c>
       <c r="O13" t="n">
         <v>-3.21</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.59</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45001.38541666666</v>
+        <v>45001.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>724.15</v>
+        <v>710</v>
       </c>
       <c r="I14" t="n">
         <v>719.1933263997103</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>15.78</v>
+        <v>13.52</v>
       </c>
       <c r="L14" t="n">
         <v>4.12</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.94</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45029.38541666666</v>
+        <v>45029.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="I15" t="n">
         <v>728.4818371704695</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.97</v>
+        <v>-3.8</v>
       </c>
       <c r="L15" t="n">
         <v>13.73</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45049.38541666666</v>
+        <v>45049.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>720.3</v>
+        <v>715</v>
       </c>
       <c r="I16" t="n">
         <v>717.3043046754451</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.27</v>
+        <v>-2.99</v>
       </c>
       <c r="L16" t="n">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="M16" t="n">
         <v>1.88</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.37</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>730.5</v>
+        <v>733.5</v>
       </c>
       <c r="I17" t="n">
         <v>731.3717322210759</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.17</v>
+        <v>-2.59</v>
       </c>
       <c r="L17" t="n">
         <v>4.75</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.79</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>763</v>
+        <v>736.1</v>
       </c>
       <c r="I18" t="n">
         <v>761.4693225683636</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K18" t="n">
-        <v>4.02</v>
+        <v>0.35</v>
       </c>
       <c r="L18" t="n">
         <v>3.12</v>
@@ -1467,7 +1682,7 @@
         <v>1.64</v>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>4.06</v>
       </c>
       <c r="O18" t="n">
         <v>0.77</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.14</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45170.38541666666</v>
+        <v>45170.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>731.85</v>
+        <v>745.1</v>
       </c>
       <c r="I19" t="n">
         <v>741.0703828878354</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.58</v>
+        <v>-1.22</v>
       </c>
       <c r="L19" t="n">
         <v>4.1</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.89</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>905.25</v>
+        <v>860.7</v>
       </c>
       <c r="I20" t="n">
         <v>893.1606157925505</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>51.83333333333334</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>21.49</v>
+        <v>15.51</v>
       </c>
       <c r="L20" t="n">
         <v>1.89</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.04</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45231.38541666666</v>
+        <v>45231.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>913.1</v>
+        <v>931.7</v>
       </c>
       <c r="I21" t="n">
         <v>929.728944989109</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.09</v>
+        <v>-8.25</v>
       </c>
       <c r="L21" t="n">
         <v>10.96</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.74</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45278.55208333334</v>
+        <v>45279.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>968.9</v>
+        <v>950</v>
       </c>
       <c r="I22" t="n">
         <v>962.4904764738542</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>3.99</v>
+        <v>1.96</v>
       </c>
       <c r="L22" t="n">
         <v>2.09</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.06</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>970</v>
+        <v>992.9</v>
       </c>
       <c r="I23" t="n">
         <v>985.1320556325118</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.11</v>
+        <v>-4.52</v>
       </c>
       <c r="L23" t="n">
-        <v>3.79</v>
+        <v>5.26</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>-1.95</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.63</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45370.55208333334</v>
+        <v>45371.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1271.9</v>
+        <v>1231.35</v>
       </c>
       <c r="I24" t="n">
         <v>1243.596153284955</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>68.16666666666667</v>
+        <v>69</v>
       </c>
       <c r="K24" t="n">
-        <v>28.1</v>
+        <v>24.02</v>
       </c>
       <c r="L24" t="n">
         <v>2.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.35</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1308</v>
+        <v>1360</v>
       </c>
       <c r="I25" t="n">
         <v>1326.364148145038</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.22</v>
+        <v>-10.45</v>
       </c>
       <c r="L25" t="n">
-        <v>8.17</v>
+        <v>10.9</v>
       </c>
       <c r="M25" t="n">
         <v>2.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.57</v>
+        <v>3.34</v>
       </c>
       <c r="O25" t="n">
         <v>-3.44</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1430.2</v>
+        <v>1399.95</v>
       </c>
       <c r="I26" t="n">
         <v>1410.562132183336</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>5.16</v>
+        <v>2.94</v>
       </c>
       <c r="L26" t="n">
         <v>4.53</v>
@@ -1923,7 +2234,7 @@
         <v>1.91</v>
       </c>
       <c r="N26" t="n">
-        <v>1.92</v>
+        <v>3.09</v>
       </c>
       <c r="O26" t="n">
         <v>3.34</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.81</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45425.55208333334</v>
+        <v>45426.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1419.4</v>
+        <v>1494.95</v>
       </c>
       <c r="I27" t="n">
         <v>1491.090384947918</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.39</v>
+        <v>-6.79</v>
       </c>
       <c r="L27" t="n">
-        <v>3.54</v>
+        <v>7.07</v>
       </c>
       <c r="M27" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="N27" t="n">
-        <v>1.98</v>
+        <v>4.62</v>
       </c>
       <c r="O27" t="n">
         <v>-3.09</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1642.05</v>
+        <v>1596.9</v>
       </c>
       <c r="I28" t="n">
         <v>1627.089997596944</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K28" t="n">
-        <v>9.84</v>
+        <v>6.82</v>
       </c>
       <c r="L28" t="n">
         <v>4.41</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45481.55208333334</v>
+        <v>45482.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1657.2</v>
+        <v>1778.3</v>
       </c>
       <c r="I29" t="n">
         <v>1711.611518615841</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.78</v>
+        <v>-11.36</v>
       </c>
       <c r="L29" t="n">
         <v>13.03</v>
@@ -2094,7 +2441,7 @@
         <v>0.59</v>
       </c>
       <c r="N29" t="n">
-        <v>6.07</v>
+        <v>12.96</v>
       </c>
       <c r="O29" t="n">
         <v>-1.83</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>13.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1711</v>
+        <v>1621.25</v>
       </c>
       <c r="I30" t="n">
         <v>1624.068465435279</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.78</v>
+        <v>-8.83</v>
       </c>
       <c r="L30" t="n">
         <v>12.59</v>
       </c>
       <c r="M30" t="n">
-        <v>1.74</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
         <v>8.66</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.73</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1713.9</v>
+        <v>1727.8</v>
       </c>
       <c r="I31" t="n">
         <v>1726.687332621954</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.71</v>
+        <v>-6.57</v>
       </c>
       <c r="L31" t="n">
         <v>7.88</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2063</v>
+        <v>1935.65</v>
       </c>
       <c r="I32" t="n">
         <v>1968.560006608001</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K32" t="n">
-        <v>19.4</v>
+        <v>12.03</v>
       </c>
       <c r="L32" t="n">
         <v>4.5</v>
@@ -2265,7 +2648,7 @@
         <v>1.28</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>6.83</v>
       </c>
       <c r="O32" t="n">
         <v>0.93</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>15.32</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45630.38541666666</v>
+        <v>45630.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1903.9</v>
+        <v>1916</v>
       </c>
       <c r="I33" t="n">
         <v>1904.433716864431</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="L33" t="n">
         <v>8.33</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.77</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45649.55208333334</v>
+        <v>45650.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1998.8</v>
+        <v>1987.35</v>
       </c>
       <c r="I34" t="n">
         <v>1989.674070974705</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>4.32</v>
+        <v>3.72</v>
       </c>
       <c r="L34" t="n">
         <v>0.72</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45653.55208333334</v>
+        <v>45656.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2058.25</v>
+        <v>2158.25</v>
       </c>
       <c r="I35" t="n">
         <v>2116.414126332256</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.57</v>
+        <v>-8.6</v>
       </c>
       <c r="L35" t="n">
-        <v>6.37</v>
+        <v>10.56</v>
       </c>
       <c r="M35" t="n">
-        <v>0.76</v>
+        <v>1.28</v>
       </c>
       <c r="N35" t="n">
-        <v>3.19</v>
+        <v>3.58</v>
       </c>
       <c r="O35" t="n">
         <v>-0.85</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2155</v>
+        <v>2065.8</v>
       </c>
       <c r="I36" t="n">
         <v>2115.512543229413</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.15</v>
+        <v>-4.28</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="M36" t="n">
         <v>0.49</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.27</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1823.1</v>
+        <v>1959.2</v>
       </c>
       <c r="I37" t="n">
         <v>1930.812218386912</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>11.75</v>
+        <v>5.16</v>
       </c>
       <c r="L37" t="n">
         <v>4.65</v>
@@ -2550,7 +2993,7 @@
         <v>2.03</v>
       </c>
       <c r="N37" t="n">
-        <v>5.01</v>
+        <v>11.49</v>
       </c>
       <c r="O37" t="n">
         <v>-2.18</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.74</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45751.38541666666</v>
+        <v>45751.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>2039.3</v>
+        <v>2030</v>
       </c>
       <c r="I38" t="n">
         <v>2033.19963174608</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>4.09</v>
+        <v>3.61</v>
       </c>
       <c r="L38" t="n">
         <v>7.43</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45818.38541666666</v>
+        <v>45818.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1621.1</v>
+        <v>1634.7</v>
       </c>
       <c r="I39" t="n">
         <v>1622.985333750028</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66.83333333333333</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>20.14</v>
+        <v>19.47</v>
       </c>
       <c r="L39" t="n">
         <v>3.67</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.37</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1632.3</v>
+        <v>1580</v>
       </c>
       <c r="I40" t="n">
         <v>1585.422114445571</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.15</v>
+        <v>-3.35</v>
       </c>
       <c r="L40" t="n">
-        <v>3.65</v>
+        <v>4.17</v>
       </c>
       <c r="M40" t="n">
         <v>2.89</v>
       </c>
       <c r="N40" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
         <v>4.12</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.78</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45838.55208333334</v>
+        <v>45839.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1643.9</v>
+        <v>1688.5</v>
       </c>
       <c r="I41" t="n">
         <v>1683.474085712261</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.04</v>
+        <v>-6.87</v>
       </c>
       <c r="L41" t="n">
-        <v>6.52</v>
+        <v>7.53</v>
       </c>
       <c r="M41" t="n">
         <v>0.48</v>
       </c>
       <c r="N41" t="n">
-        <v>1.44</v>
+        <v>4.02</v>
       </c>
       <c r="O41" t="n">
         <v>-2.4</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45859.55208333334</v>
+        <v>45860.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1815</v>
+        <v>1765.6</v>
       </c>
       <c r="I42" t="n">
         <v>1788.434901901787</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K42" t="n">
-        <v>7.49</v>
+        <v>4.57</v>
       </c>
       <c r="L42" t="n">
         <v>3.37</v>
@@ -2835,7 +3338,7 @@
         <v>0.65</v>
       </c>
       <c r="N42" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="O42" t="n">
         <v>4.02</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.27</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45875.38541666666</v>
+        <v>45875.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1748</v>
+        <v>1786.3</v>
       </c>
       <c r="I43" t="n">
         <v>1785.936705302405</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>-1.17</v>
       </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>3.36</v>
       </c>
       <c r="M43" t="n">
         <v>0.41</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.48</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45908.38541666666</v>
+        <v>45908.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1891.2</v>
+        <v>1883.3</v>
       </c>
       <c r="I44" t="n">
         <v>1888.340641370296</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K44" t="n">
-        <v>5.87</v>
+        <v>5.43</v>
       </c>
       <c r="L44" t="n">
         <v>4.3</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.85</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45917.55208333334</v>
+        <v>45918.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1946.9</v>
+        <v>1959.2</v>
       </c>
       <c r="I45" t="n">
         <v>1958.866467772811</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.38</v>
+        <v>-4.03</v>
       </c>
       <c r="L45" t="n">
-        <v>3.49</v>
+        <v>5.13</v>
       </c>
       <c r="M45" t="n">
         <v>0.83</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.31</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1925.1</v>
+        <v>1890.8</v>
       </c>
       <c r="I46" t="n">
         <v>1911.277645898564</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.74</v>
+        <v>-3.49</v>
       </c>
       <c r="L46" t="n">
-        <v>2.01</v>
+        <v>3.6</v>
       </c>
       <c r="M46" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="N46" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="O46" t="n">
         <v>0.83</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.88</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1914.6</v>
+        <v>1962.6</v>
       </c>
       <c r="I47" t="n">
         <v>1958.126305478587</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.26</v>
+        <v>-3.8</v>
       </c>
       <c r="L47" t="n">
         <v>3.97</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.67</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45964.38541666666</v>
+        <v>45964.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1938</v>
+        <v>1902.1</v>
       </c>
       <c r="I48" t="n">
         <v>1918.170832324622</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.25</v>
+        <v>-3.08</v>
       </c>
       <c r="L48" t="n">
-        <v>2.53</v>
+        <v>3.12</v>
       </c>
       <c r="M48" t="n">
         <v>0.13</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.35</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46003.38541666666</v>
+        <v>46003.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1776.5</v>
+        <v>1802</v>
       </c>
       <c r="I49" t="n">
         <v>1794.715661410199</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>6.6</v>
+        <v>5.26</v>
       </c>
       <c r="L49" t="n">
         <v>6.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.19</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1853</v>
+        <v>1773</v>
       </c>
       <c r="I50" t="n">
         <v>1780.549460160279</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>2.83</v>
+        <v>-1.61</v>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>2.54</v>
       </c>
       <c r="M50" t="n">
         <v>0.89</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O50" t="n">
         <v>2.91</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.47</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1780</v>
+        <v>1813.8</v>
       </c>
       <c r="I51" t="n">
         <v>1788.793533291554</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.39</v>
+        <v>-2.3</v>
       </c>
       <c r="L51" t="n">
         <v>4.96</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46042.38541666666</v>
+        <v>46042.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>1752.3</v>
+        <v>1735.5</v>
       </c>
       <c r="I52" t="n">
         <v>1737.883525778442</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.39</v>
+        <v>-4.32</v>
       </c>
       <c r="L52" t="n">
         <v>4.76</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.37</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1729</v>
+        <v>1800.5</v>
       </c>
       <c r="I53" t="n">
         <v>1776.511165876776</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>0.37</v>
+        <v>-3.75</v>
       </c>
       <c r="L53" t="n">
-        <v>2.09</v>
+        <v>4.47</v>
       </c>
       <c r="M53" t="n">
         <v>0.61</v>
       </c>
       <c r="N53" t="n">
-        <v>3.23</v>
+        <v>5.38</v>
       </c>
       <c r="O53" t="n">
         <v>-1.84</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>11.14</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1936</v>
+        <v>1890.5</v>
       </c>
       <c r="I54" t="n">
         <v>1918.498052348596</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>7.53</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
         <v>5.63</v>
       </c>
       <c r="M54" t="n">
-        <v>1.68</v>
+        <v>3.78</v>
       </c>
       <c r="N54" t="n">
         <v>2.72</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.12</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46121.55208333334</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1645</v>
+        <v>1689</v>
       </c>
       <c r="I55" t="n">
         <v>1668.158693367727</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K55" t="n">
-        <v>12.99</v>
+        <v>10.66</v>
       </c>
       <c r="L55" t="n">
         <v>4.95</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.44</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1813</v>
+        <v>1752.4</v>
       </c>
       <c r="I56" t="n">
         <v>1774.988071384882</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K56" t="n">
-        <v>7.34</v>
+        <v>3.75</v>
       </c>
       <c r="L56" t="n">
         <v>3.41</v>
@@ -3633,7 +4304,7 @@
         <v>3.17</v>
       </c>
       <c r="N56" t="n">
-        <v>3.19</v>
+        <v>3.47</v>
       </c>
       <c r="O56" t="n">
         <v>2.74</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.75</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1624.7</v>
+        <v>1690.4</v>
       </c>
       <c r="I57" t="n">
         <v>1646.001203589823</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>7.29</v>
+        <v>3.54</v>
       </c>
       <c r="L57" t="n">
         <v>4.19</v>
@@ -3690,7 +4373,7 @@
         <v>2.29</v>
       </c>
       <c r="N57" t="n">
-        <v>2.68</v>
+        <v>4.39</v>
       </c>
       <c r="O57" t="n">
         <v>-3.47</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.39</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1620</v>
+        <v>1610.2</v>
       </c>
       <c r="I58" t="n">
         <v>1611.72784463047</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.16</v>
+        <v>-4.74</v>
       </c>
       <c r="L58" t="n">
-        <v>4.16</v>
+        <v>5.05</v>
       </c>
       <c r="M58" t="n">
         <v>0.2</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1663</v>
+        <v>1702.9</v>
       </c>
       <c r="I59" t="n">
         <v>1668.573128139009</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.28</v>
+        <v>-5.76</v>
       </c>
       <c r="L59" t="n">
-        <v>3.72</v>
+        <v>6.22</v>
       </c>
       <c r="M59" t="n">
         <v>0.63</v>
       </c>
       <c r="N59" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="O59" t="n">
         <v>-0.31</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.91</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46225.38541666666</v>
+        <v>46225.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1667.9</v>
+        <v>1660.9</v>
       </c>
       <c r="I60" t="n">
         <v>1662.510565042493</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.06</v>
+        <v>-2.47</v>
       </c>
       <c r="L60" t="n">
         <v>4.19</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.68</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46237.38541666666</v>
+        <v>46237.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1707.4</v>
+        <v>1729.5</v>
       </c>
       <c r="I61" t="n">
         <v>1720.335482115895</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.8</v>
+        <v>-4.13</v>
       </c>
       <c r="L61" t="n">
-        <v>3.62</v>
+        <v>4.16</v>
       </c>
       <c r="M61" t="n">
         <v>0.71</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.67</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46240.38541666666</v>
+        <v>46240.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1655.5</v>
+        <v>1571</v>
       </c>
       <c r="I62" t="n">
         <v>1631.509021141895</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.28</v>
+        <v>-9.16</v>
       </c>
       <c r="L62" t="n">
-        <v>5.45</v>
+        <v>10.41</v>
       </c>
       <c r="M62" t="n">
         <v>0.08</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.17</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1514</v>
+        <v>1556.6</v>
       </c>
       <c r="I63" t="n">
         <v>1516.700363807632</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>3.63</v>
+        <v>0.92</v>
       </c>
       <c r="L63" t="n">
         <v>5.91</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1518</v>
+        <v>1462</v>
       </c>
       <c r="I64" t="n">
         <v>1488.017482771134</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.48</v>
+        <v>-6.08</v>
       </c>
       <c r="L64" t="n">
-        <v>5.43</v>
+        <v>6.87</v>
       </c>
       <c r="M64" t="n">
         <v>1.03</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1508</v>
+        <v>1565</v>
       </c>
       <c r="I65" t="n">
         <v>1549.226736239763</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.15</v>
+        <v>-7.05</v>
       </c>
       <c r="L65" t="n">
-        <v>3.76</v>
+        <v>7.98</v>
       </c>
       <c r="M65" t="n">
         <v>1.44</v>
       </c>
       <c r="N65" t="n">
-        <v>3.64</v>
+        <v>4.24</v>
       </c>
       <c r="O65" t="n">
         <v>-4.15</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.73</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1563.8</v>
+        <v>1489.2</v>
       </c>
       <c r="I66" t="n">
         <v>1520.19640681348</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.08</v>
+        <v>-4.84</v>
       </c>
       <c r="L66" t="n">
-        <v>4.07</v>
+        <v>4.84</v>
       </c>
       <c r="M66" t="n">
         <v>0.96</v>
       </c>
       <c r="N66" t="n">
-        <v>2.37</v>
+        <v>4.27</v>
       </c>
       <c r="O66" t="n">
         <v>4.24</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,12 @@
       <c r="Q67" t="n">
         <v>6</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7244,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.2</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.63</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.51</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.1</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.73</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.12</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="21">
@@ -6535,7 +7344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6545,7 +7354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -6555,7 +7364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.49</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.66</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
